--- a/resource/元数据_测试.xlsx
+++ b/resource/元数据_测试.xlsx
@@ -257,10 +257,10 @@
     <t>cm</t>
   </si>
   <si>
-    <t>SSCEQPA2</t>
-  </si>
-  <si>
-    <t>SSCEQPA3</t>
+    <t>SSCEQPA'2</t>
+  </si>
+  <si>
+    <t>SSCEQPA"3</t>
   </si>
   <si>
     <t>SSCEQPA4</t>
